--- a/data/raw/LAPE_cadastros.xlsx
+++ b/data/raw/LAPE_cadastros.xlsx
@@ -11,9 +11,10 @@
     <sheet name="Linhas de Pesquisa" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Instituições" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Publicações" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Eventos" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Motivos de recusa" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Instruções" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Projetos" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Eventos" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Motivos de recusa" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Instruções" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -432,22 +433,24 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M18"/>
+  <dimension ref="A1:O18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
-    <col width="16" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="16" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -473,45 +476,55 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>Titulação</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>Linha de pesquisa</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Instituição</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Lattes</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>ORCID</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>E-mail</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Telefone</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Data de entrada</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Data de saída</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Externo</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Ativo</t>
         </is>
@@ -528,12 +541,12 @@
           <t>Alexandro</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>Não</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
@@ -550,12 +563,12 @@
           <t>Anderson</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>Não</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
@@ -572,12 +585,12 @@
           <t>Andrade</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>Não</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
@@ -594,12 +607,12 @@
           <t>Angelise</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>Não</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
@@ -616,12 +629,12 @@
           <t>Ariane</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>Não</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
@@ -638,12 +651,12 @@
           <t>Camile</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>Não</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
@@ -660,12 +673,12 @@
           <t>Carla</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>Não</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
@@ -682,12 +695,12 @@
           <t>Henrique</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>Não</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
@@ -704,12 +717,12 @@
           <t>Henrique Fukumasa</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>Não</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
@@ -726,12 +739,12 @@
           <t>Juliana</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="N11" t="inlineStr">
         <is>
           <t>Não</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="O11" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
@@ -748,12 +761,12 @@
           <t>Letícia</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>Não</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
@@ -770,12 +783,12 @@
           <t>Loiane</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="N13" t="inlineStr">
         <is>
           <t>Não</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
+      <c r="O13" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
@@ -792,12 +805,12 @@
           <t>Luiza</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="N14" t="inlineStr">
         <is>
           <t>Não</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr">
+      <c r="O14" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
@@ -814,12 +827,12 @@
           <t>Marcele</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
+      <c r="N15" t="inlineStr">
         <is>
           <t>Não</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr">
+      <c r="O15" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
@@ -836,12 +849,12 @@
           <t>Marina</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
+      <c r="N16" t="inlineStr">
         <is>
           <t>Não</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr">
+      <c r="O16" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
@@ -858,12 +871,12 @@
           <t>Nayara</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr">
+      <c r="N17" t="inlineStr">
         <is>
           <t>Não</t>
         </is>
       </c>
-      <c r="M17" t="inlineStr">
+      <c r="O17" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
@@ -880,12 +893,12 @@
           <t>Vilarino</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr">
+      <c r="N18" t="inlineStr">
         <is>
           <t>Não</t>
         </is>
       </c>
-      <c r="M18" t="inlineStr">
+      <c r="O18" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
@@ -1330,6 +1343,184 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="52" customWidth="1" min="2" max="2"/>
+    <col width="52" customWidth="1" min="3" max="3"/>
+    <col width="29" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="15" customWidth="1" min="12" max="12"/>
+    <col width="28" customWidth="1" min="13" max="13"/>
+    <col width="28" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Código</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Projeto</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Descrição</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Linha de pesquisa</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Coordenador</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Tipo</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Financiador</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Processo</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Valor</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Início</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Término</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Situação</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Parecer ético</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Integrantes</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Link</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>PROJ-01</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Exercício físico e saúde mental em mulheres com fibromialgia</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Ensaio clínico randomizado com treinamento resistido.</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Dor Crônica e Fibromialgia</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Alexandro Andrade</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Pesquisa</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>CNPq</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>409XXX/2024-0</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>120000</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>2024-03-01</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>2027-02-28</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>Em andamento</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>CAAE 00000000.0.0000.0000</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>Andrade; Vilarino; Loiane</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:O2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
     <col width="24" customWidth="1" min="2" max="2"/>
     <col width="37" customWidth="1" min="3" max="3"/>
     <col width="19" customWidth="1" min="4" max="4"/>
@@ -1486,7 +1677,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1709,13 +1900,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -1793,35 +1984,47 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Eventos</t>
+          <t>Projetos</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Reuniões, coletas, defesas, congressos, cursos. Alimentam o calendário, a análise temporal e o mapa.</t>
+          <t>Um projeto por linha. A coluna 'Integrantes' aceita vários nomes separados por ponto e vírgula — é o que liga cada pesquisador aos projetos de que participa.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>Eventos</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Reuniões, coletas, defesas, congressos, cursos. Alimentam o calendário, a análise temporal e o mapa.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>Motivos de recusa</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>Catálogo controlado. Use exatamente o mesmo texto na coluna 'Motivo/observação' da aba de tentativas de submissão.</t>
         </is>
       </c>
     </row>
-    <row r="10"/>
-    <row r="11">
-      <c r="A11" t="inlineStr">
+    <row r="11"/>
+    <row r="12">
+      <c r="A12" t="inlineStr">
         <is>
           <t>Importante</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>Não renomeie as abas. Colunas podem ser reordenadas e novas colunas podem ser acrescentadas — o importador reconhece as colunas pelo nome.</t>
         </is>
